--- a/manuscript_tables_updated.xlsx
+++ b/manuscript_tables_updated.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1 - Demographics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suppl - Questionnaire Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1 - By Outcome" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -90,7 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -469,7 +467,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 1. Patient Demographics, Clinical Characteristics, and Prior Treatment History (N=107)</t>
+          <t>Table 1. Patient Demographics, Prior Treatment, and Clinical Characteristics (N=107)</t>
         </is>
       </c>
     </row>
@@ -568,64 +566,88 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wart location</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
+          <t>Current/past smoker, n (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>15 (14.0%)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>9 (19.6%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>6 (9.8%)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0.170</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Palmoplantar/other</t>
+          <t>Hyperhidrosis, n (%)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>70 (65.4%)</t>
+          <t>8 (7.5%)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>29 (63.0%)</t>
+          <t>2 (4.3%)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>41 (67.2%)</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
+          <t>6 (9.8%)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0.462</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Condylomata</t>
+          <t>HPV vaccination, n (%)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>37 (34.6%)</t>
+          <t>17 (15.9%)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>17 (37.0%)</t>
+          <t>7 (15.2%)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>20 (32.8%)</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
+          <t>10 (16.4%)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Wart location</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
@@ -636,22 +658,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1064nm only</t>
+          <t xml:space="preserve">  Palmoplantar/other</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>48 (44.9%)</t>
+          <t>70 (65.4%)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>26 (56.5%)</t>
+          <t>29 (63.0%)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22 (36.1%)</t>
+          <t>41 (67.2%)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
@@ -659,229 +681,217 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2940nm only</t>
+          <t xml:space="preserve">  Condylomata</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>24 (22.4%)</t>
+          <t>37 (34.6%)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>9 (19.6%)</t>
+          <t>17 (37.0%)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>15 (24.6%)</t>
+          <t>20 (32.8%)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Combination</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>33 (30.8%)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>10 (21.7%)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>23 (37.7%)</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Treatment sessions (mean ± SD)</t>
+          <t xml:space="preserve">  1064nm only</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>6.7 ± 5.4</t>
+          <t>48 (44.9%)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>4.3 ± 2.9</t>
+          <t>26 (56.5%)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>8.6 ± 6.1</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
+          <t>22 (36.1%)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Prior Treatment History</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2940nm only</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>24 (22.4%)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>9 (19.6%)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>15 (24.6%)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prior cryotherapy, n (%)</t>
+          <t xml:space="preserve">  Combination</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>76 (71.0%)</t>
+          <t>33 (30.8%)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>33 (71.7%)</t>
+          <t>10 (21.7%)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>43 (70.5%)</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
+          <t>23 (37.7%)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Prior electrocautery, n (%)</t>
+          <t>Treatment sessions (mean ± SD)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>16 (15.0%)</t>
+          <t>6.7 ± 5.4</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>9 (19.6%)</t>
+          <t>4.3 ± 2.9</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>7 (11.5%)</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
+          <t>8.6 ± 6.1</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Prior topical therapy, n (%)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>62 (57.9%)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>26 (56.5%)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>36 (59.0%)</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>0.845</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Prior Treatment History</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Verrumal</t>
+          <t>Prior cryotherapy, n (%)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>39 (36.4%)</t>
+          <t>76 (71.0%)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>15 (32.6%)</t>
+          <t>33 (71.7%)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>24 (39.3%)</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
+          <t>43 (70.5%)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Salatac</t>
+          <t>Prior topical therapy, n (%)</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>19 (17.8%)</t>
+          <t>62 (57.9%)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>8 (17.4%)</t>
+          <t>26 (56.5%)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>11 (18.0%)</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
+          <t>36 (59.0%)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0.845</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Condylox</t>
+          <t xml:space="preserve">  Verrumal</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>10 (9.3%)</t>
+          <t>39 (36.4%)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>4 (8.7%)</t>
+          <t>15 (32.6%)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>6 (9.8%)</t>
+          <t>24 (39.3%)</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
@@ -889,22 +899,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Bliyabelet</t>
+          <t xml:space="preserve">  Salatac</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>9 (8.4%)</t>
+          <t>19 (17.8%)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>3 (6.5%)</t>
+          <t>8 (17.4%)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>6 (9.8%)</t>
+          <t>11 (18.0%)</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
@@ -912,17 +922,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gardasil 9 (therapeutic), n (%)</t>
+          <t xml:space="preserve">  Condylox</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>11 (10.3%)</t>
+          <t>10 (9.3%)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>5 (10.9%)</t>
+          <t>4 (8.7%)</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -935,610 +945,107 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>No. prior topical agents (mean ± SD)</t>
+          <t>Prior electrocautery, n (%)</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>0.8 ± 0.8</t>
+          <t>16 (15.0%)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>0.7 ± 0.7</t>
+          <t>9 (19.6%)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>0.8 ± 0.8</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>0.380</t>
-        </is>
-      </c>
+          <t>7 (11.5%)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Comorbidities</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Gardasil 9 (therapeutic), n (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>11 (10.3%)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>5 (10.9%)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>6 (9.8%)</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>No comorbidities, n (%)</t>
+          <t>Prior wart history, n (%)</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>60 (56.1%)</t>
+          <t>22 (20.6%)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>27 (58.7%)</t>
+          <t>9 (19.6%)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>33 (54.1%)</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
+          <t>13 (21.3%)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Smoking</t>
+          <t>No. prior topical agents (mean ± SD)</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>21 (19.6%)</t>
+          <t>0.8 ± 0.8</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>8 (17.4%)</t>
+          <t>0.7 ± 0.7</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>13 (21.3%)</t>
+          <t>0.8 ± 0.8</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.806</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Hypertension</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>12 (11.2%)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>4 (8.7%)</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>8 (13.1%)</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>0.549</t>
+          <t>0.380</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Metabolic disease</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>15 (14.0%)</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>6 (13.0%)</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>9 (14.8%)</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Skin malignancy</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>9 (8.4%)</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>2 (4.3%)</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>7 (11.5%)</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>0.295</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Autoimmune disease</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>6 (5.6%)</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>2 (4.3%)</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>4 (6.6%)</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>0.698</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Endocrine disease</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>5 (4.7%)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>1 (2.2%)</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>4 (6.6%)</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>0.388</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Obesity</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>5 (4.7%)</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>2 (4.3%)</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>3 (4.9%)</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BPH</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>3 (2.8%)</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>3 (4.9%)</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>0.258</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Values are n (%) or mean ± SD. p-values by Fisher's exact test or Mann-Whitney U test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>NEW rows highlighted in blue indicate data added from updated patient records.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Supplementary Table S1. Patient-Reported Questionnaire Data (subset with available data)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>n with data</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Healed</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Not Healed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>HPV Vaccination Status</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Not vaccinated</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>43 (58.1%)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Partially vaccinated</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>8 (10.8%)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fully vaccinated</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>9 (12.2%)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unknown</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>14 (18.9%)</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Smoking (self-reported)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Yes</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>15 (19.7%)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  No</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>61 (80.3%)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Prior Wart History</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Yes</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>22 (29.3%)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  No</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>53 (70.7%)</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Hyperhidrosis</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Yes</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>8 (11.8%)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  No</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>60 (88.2%)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Data from patient-reported questionnaires. Not all patients completed the questionnaire.</t>
         </is>
       </c>
     </row>

--- a/manuscript_tables_updated.xlsx
+++ b/manuscript_tables_updated.xlsx
@@ -471,6 +471,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -663,12 +664,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>70 (65.4%)</t>
+          <t>69 (64.5%)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>29 (63.0%)</t>
+          <t>28 (60.9%)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -686,12 +687,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>37 (34.6%)</t>
+          <t>38 (35.5%)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>17 (37.0%)</t>
+          <t>18 (39.1%)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -720,17 +721,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>48 (44.9%)</t>
+          <t>50 (46.7%)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>26 (56.5%)</t>
+          <t>27 (58.7%)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22 (36.1%)</t>
+          <t>23 (37.7%)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
@@ -1042,6 +1043,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
